--- a/Pre-operacional.xlsx
+++ b/Pre-operacional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laptod\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XJuan\source\repos\AutoCheckAML\Docs-AutoCheck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14BF019-07D4-42C6-A9E2-42C83874F67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A2C03E-1538-477C-A669-9DBC2FA9EA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -878,7 +878,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -888,16 +888,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -910,28 +919,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -992,9 +986,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1032,7 +1026,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1138,7 +1132,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1280,7 +1274,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1292,52 +1286,52 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1348,797 +1342,883 @@
         <v>4</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7">
         <v>39</v>
       </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="G17" s="12"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="G18" s="12"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="G19" s="12"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="G21" s="12"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="G25" s="12"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="G26" s="12"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="G27" s="12"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="G28" s="12"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="G30" s="12"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="G32" s="12"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="G33" s="12"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="G35" s="12"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="G36" s="12"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="G37" s="12"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="G38" s="12"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="G39" s="12"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+    </row>
+    <row r="43" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="11"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="G48" s="12"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="G49" s="12"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="G50" s="12"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+      <c r="G51" s="12"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="11"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="G52" s="12"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
       <c r="E53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G3:H3"/>
@@ -2163,92 +2243,6 @@
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G46:J46"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A52:D52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
@@ -2258,23 +2252,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87089318-8902-41A0-BEA7-F24B0515644C}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E1" t="s">
